--- a/Customer_Info_MK.xlsx
+++ b/Customer_Info_MK.xlsx
@@ -3846,7 +3846,7 @@
     <t>ТОВ "Центр мистецтва реабілітації Реарт"</t>
   </si>
   <si>
-    <t>DEСentrMystetstvaReabilitatsiiReart</t>
+    <t>DECentrMystetstvaReabilitatsiiReart</t>
   </si>
   <si>
     <t>F499417C-7CB0-423E-AB69-4A1258B47A05</t>
